--- a/generation_results.xlsx
+++ b/generation_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\School\master's\diplomovka\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\School\master\diplomovka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94A327A0-3F02-4C64-AB8E-880AF4FFAAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6624DC95-AD44-4618-9E8F-856BF9B6F540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="2" xr2:uid="{37E1C211-AA4A-4906-B2F7-D5BD0B5E9EA7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{37E1C211-AA4A-4906-B2F7-D5BD0B5E9EA7}"/>
   </bookViews>
   <sheets>
     <sheet name="2-states" sheetId="6" r:id="rId1"/>
@@ -89,7 +89,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00000E+00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,8 +121,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -153,8 +159,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -264,11 +276,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -329,10 +354,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -341,7 +363,25 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -714,6 +754,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -721,7 +762,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1181,6 +1221,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1188,7 +1229,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1497,6 +1537,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1504,7 +1545,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1706,6 +1746,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1713,7 +1754,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2137,6 +2177,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2144,7 +2185,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2632,6 +2672,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2639,7 +2680,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2744,7 +2784,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="sk-SK"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2970,6 +3010,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2977,7 +3018,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3211,6 +3251,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3218,7 +3259,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3552,6 +3592,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3559,7 +3600,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4057,6 +4097,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4064,7 +4105,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4397,6 +4437,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4404,7 +4445,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4854,6 +4894,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4861,7 +4902,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5070,6 +5110,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5077,7 +5118,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5443,6 +5483,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5450,7 +5491,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5948,6 +5988,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5955,7 +5996,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6288,6 +6328,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6295,7 +6336,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6497,6 +6537,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6504,7 +6545,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6696,52 +6736,52 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>65536</c:v>
+                  <c:v>131072</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>121472</c:v>
+                  <c:v>108872</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>77164</c:v>
+                  <c:v>83868</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>95748</c:v>
+                  <c:v>91320</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>68892</c:v>
+                  <c:v>58356</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>58044</c:v>
+                  <c:v>77712</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>70776</c:v>
+                  <c:v>75120</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>87768</c:v>
+                  <c:v>58008</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38928</c:v>
+                  <c:v>38784</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38784</c:v>
+                  <c:v>62712</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>62712</c:v>
+                  <c:v>61176</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>61176</c:v>
+                  <c:v>35760</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>35760</c:v>
+                  <c:v>66864</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>66864</c:v>
+                  <c:v>19104</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>19104</c:v>
+                  <c:v>79848</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>79848</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7000,6 +7040,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7007,7 +7048,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7588,6 +7628,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7595,7 +7636,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7700,7 +7740,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="sk-SK"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -7788,31 +7828,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>138440</c:v>
+                  <c:v>147656</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>163616</c:v>
+                  <c:v>203120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>165480</c:v>
+                  <c:v>241968</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>206256</c:v>
+                  <c:v>233496</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>184488</c:v>
+                  <c:v>168624</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>144264</c:v>
+                  <c:v>35328</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>31104</c:v>
+                  <c:v>16944</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>13632</c:v>
+                  <c:v>1440</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1296</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -7974,6 +8014,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7981,7 +8022,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8215,6 +8255,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8222,7 +8263,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8604,6 +8644,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8611,7 +8652,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8716,7 +8756,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="sk-SK"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -8918,6 +8958,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8925,7 +8966,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9516,6 +9556,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9523,7 +9564,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9904,6 +9944,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9911,7 +9952,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10120,6 +10160,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -10127,7 +10168,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10769,6 +10809,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -10776,7 +10817,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -11522,6 +11562,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -11529,7 +11570,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -11634,7 +11674,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="sk-SK"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -12005,6 +12045,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -12012,7 +12053,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -12246,6 +12286,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -12253,7 +12294,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -13183,6 +13223,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -13190,7 +13231,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -14245,6 +14285,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -14252,7 +14293,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -14357,7 +14397,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="sk-SK"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -14920,6 +14960,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -14927,7 +14968,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -15161,6 +15201,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -15168,7 +15209,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -15402,6 +15442,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -15409,7 +15450,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -16915,6 +16955,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -16922,7 +16963,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -18573,6 +18613,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -18580,7 +18621,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -18685,7 +18725,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="sk-SK"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -19632,6 +19672,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -19639,7 +19680,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -19873,6 +19913,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -19880,7 +19921,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -20190,6 +20230,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -20197,7 +20238,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -20657,6 +20697,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -20664,7 +20705,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -20973,6 +21013,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -20980,7 +21021,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -21189,6 +21229,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -21196,7 +21237,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -21506,6 +21546,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -21513,7 +21554,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -47696,50 +47736,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:42" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="24"/>
-      <c r="AA2" s="24"/>
-      <c r="AB2" s="24"/>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="24"/>
-      <c r="AF2" s="24"/>
-      <c r="AG2" s="24"/>
-      <c r="AH2" s="24"/>
-      <c r="AI2" s="24"/>
-      <c r="AJ2" s="24"/>
-      <c r="AK2" s="24"/>
-      <c r="AL2" s="24"/>
-      <c r="AM2" s="24"/>
-      <c r="AN2" s="24"/>
-      <c r="AO2" s="24"/>
-      <c r="AP2" s="24"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="23"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
+      <c r="AH2" s="23"/>
+      <c r="AI2" s="23"/>
+      <c r="AJ2" s="23"/>
+      <c r="AK2" s="23"/>
+      <c r="AL2" s="23"/>
+      <c r="AM2" s="23"/>
+      <c r="AN2" s="23"/>
+      <c r="AO2" s="23"/>
+      <c r="AP2" s="23"/>
     </row>
     <row r="3" spans="1:42" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
@@ -47775,21 +47815,21 @@
       <c r="AA3" s="21"/>
       <c r="AB3" s="21"/>
       <c r="AC3" s="21"/>
-      <c r="AD3" s="22" t="s">
+      <c r="AD3" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="AE3" s="22"/>
-      <c r="AF3" s="22"/>
-      <c r="AG3" s="22"/>
-      <c r="AH3" s="22"/>
-      <c r="AI3" s="22"/>
-      <c r="AJ3" s="22"/>
-      <c r="AK3" s="22"/>
-      <c r="AL3" s="22"/>
-      <c r="AM3" s="22"/>
-      <c r="AN3" s="22"/>
-      <c r="AO3" s="22"/>
-      <c r="AP3" s="23"/>
+      <c r="AE3" s="25"/>
+      <c r="AF3" s="25"/>
+      <c r="AG3" s="25"/>
+      <c r="AH3" s="25"/>
+      <c r="AI3" s="25"/>
+      <c r="AJ3" s="25"/>
+      <c r="AK3" s="25"/>
+      <c r="AL3" s="25"/>
+      <c r="AM3" s="25"/>
+      <c r="AN3" s="25"/>
+      <c r="AO3" s="25"/>
+      <c r="AP3" s="26"/>
     </row>
     <row r="7" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:42" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -47915,50 +47955,50 @@
       </c>
     </row>
     <row r="35" spans="1:42" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="25" t="s">
+      <c r="A35" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="25"/>
-      <c r="K35" s="25"/>
-      <c r="L35" s="25"/>
-      <c r="M35" s="25"/>
-      <c r="N35" s="25"/>
-      <c r="O35" s="25"/>
-      <c r="P35" s="25"/>
-      <c r="Q35" s="25"/>
-      <c r="R35" s="25"/>
-      <c r="S35" s="25"/>
-      <c r="T35" s="25"/>
-      <c r="U35" s="25"/>
-      <c r="V35" s="25"/>
-      <c r="W35" s="25"/>
-      <c r="X35" s="25"/>
-      <c r="Y35" s="25"/>
-      <c r="Z35" s="25"/>
-      <c r="AA35" s="25"/>
-      <c r="AB35" s="25"/>
-      <c r="AC35" s="25"/>
-      <c r="AD35" s="25"/>
-      <c r="AE35" s="25"/>
-      <c r="AF35" s="25"/>
-      <c r="AG35" s="25"/>
-      <c r="AH35" s="25"/>
-      <c r="AI35" s="25"/>
-      <c r="AJ35" s="25"/>
-      <c r="AK35" s="25"/>
-      <c r="AL35" s="25"/>
-      <c r="AM35" s="25"/>
-      <c r="AN35" s="25"/>
-      <c r="AO35" s="25"/>
-      <c r="AP35" s="25"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="24"/>
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24"/>
+      <c r="N35" s="24"/>
+      <c r="O35" s="24"/>
+      <c r="P35" s="24"/>
+      <c r="Q35" s="24"/>
+      <c r="R35" s="24"/>
+      <c r="S35" s="24"/>
+      <c r="T35" s="24"/>
+      <c r="U35" s="24"/>
+      <c r="V35" s="24"/>
+      <c r="W35" s="24"/>
+      <c r="X35" s="24"/>
+      <c r="Y35" s="24"/>
+      <c r="Z35" s="24"/>
+      <c r="AA35" s="24"/>
+      <c r="AB35" s="24"/>
+      <c r="AC35" s="24"/>
+      <c r="AD35" s="24"/>
+      <c r="AE35" s="24"/>
+      <c r="AF35" s="24"/>
+      <c r="AG35" s="24"/>
+      <c r="AH35" s="24"/>
+      <c r="AI35" s="24"/>
+      <c r="AJ35" s="24"/>
+      <c r="AK35" s="24"/>
+      <c r="AL35" s="24"/>
+      <c r="AM35" s="24"/>
+      <c r="AN35" s="24"/>
+      <c r="AO35" s="24"/>
+      <c r="AP35" s="24"/>
     </row>
     <row r="36" spans="1:42" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="20" t="s">
@@ -47994,21 +48034,21 @@
       <c r="AA36" s="21"/>
       <c r="AB36" s="21"/>
       <c r="AC36" s="21"/>
-      <c r="AD36" s="22" t="s">
+      <c r="AD36" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="AE36" s="22"/>
-      <c r="AF36" s="22"/>
-      <c r="AG36" s="22"/>
-      <c r="AH36" s="22"/>
-      <c r="AI36" s="22"/>
-      <c r="AJ36" s="22"/>
-      <c r="AK36" s="22"/>
-      <c r="AL36" s="22"/>
-      <c r="AM36" s="22"/>
-      <c r="AN36" s="22"/>
-      <c r="AO36" s="22"/>
-      <c r="AP36" s="23"/>
+      <c r="AE36" s="25"/>
+      <c r="AF36" s="25"/>
+      <c r="AG36" s="25"/>
+      <c r="AH36" s="25"/>
+      <c r="AI36" s="25"/>
+      <c r="AJ36" s="25"/>
+      <c r="AK36" s="25"/>
+      <c r="AL36" s="25"/>
+      <c r="AM36" s="25"/>
+      <c r="AN36" s="25"/>
+      <c r="AO36" s="25"/>
+      <c r="AP36" s="26"/>
     </row>
     <row r="41" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="42" spans="1:42" ht="22.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -48134,50 +48174,50 @@
       </c>
     </row>
     <row r="68" spans="1:42" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="25" t="s">
+      <c r="A68" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B68" s="25"/>
-      <c r="C68" s="25"/>
-      <c r="D68" s="25"/>
-      <c r="E68" s="25"/>
-      <c r="F68" s="25"/>
-      <c r="G68" s="25"/>
-      <c r="H68" s="25"/>
-      <c r="I68" s="25"/>
-      <c r="J68" s="25"/>
-      <c r="K68" s="25"/>
-      <c r="L68" s="25"/>
-      <c r="M68" s="25"/>
-      <c r="N68" s="25"/>
-      <c r="O68" s="25"/>
-      <c r="P68" s="25"/>
-      <c r="Q68" s="25"/>
-      <c r="R68" s="25"/>
-      <c r="S68" s="25"/>
-      <c r="T68" s="25"/>
-      <c r="U68" s="25"/>
-      <c r="V68" s="25"/>
-      <c r="W68" s="25"/>
-      <c r="X68" s="25"/>
-      <c r="Y68" s="25"/>
-      <c r="Z68" s="25"/>
-      <c r="AA68" s="25"/>
-      <c r="AB68" s="25"/>
-      <c r="AC68" s="25"/>
-      <c r="AD68" s="25"/>
-      <c r="AE68" s="25"/>
-      <c r="AF68" s="25"/>
-      <c r="AG68" s="25"/>
-      <c r="AH68" s="25"/>
-      <c r="AI68" s="25"/>
-      <c r="AJ68" s="25"/>
-      <c r="AK68" s="25"/>
-      <c r="AL68" s="25"/>
-      <c r="AM68" s="25"/>
-      <c r="AN68" s="25"/>
-      <c r="AO68" s="25"/>
-      <c r="AP68" s="25"/>
+      <c r="B68" s="24"/>
+      <c r="C68" s="24"/>
+      <c r="D68" s="24"/>
+      <c r="E68" s="24"/>
+      <c r="F68" s="24"/>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="24"/>
+      <c r="J68" s="24"/>
+      <c r="K68" s="24"/>
+      <c r="L68" s="24"/>
+      <c r="M68" s="24"/>
+      <c r="N68" s="24"/>
+      <c r="O68" s="24"/>
+      <c r="P68" s="24"/>
+      <c r="Q68" s="24"/>
+      <c r="R68" s="24"/>
+      <c r="S68" s="24"/>
+      <c r="T68" s="24"/>
+      <c r="U68" s="24"/>
+      <c r="V68" s="24"/>
+      <c r="W68" s="24"/>
+      <c r="X68" s="24"/>
+      <c r="Y68" s="24"/>
+      <c r="Z68" s="24"/>
+      <c r="AA68" s="24"/>
+      <c r="AB68" s="24"/>
+      <c r="AC68" s="24"/>
+      <c r="AD68" s="24"/>
+      <c r="AE68" s="24"/>
+      <c r="AF68" s="24"/>
+      <c r="AG68" s="24"/>
+      <c r="AH68" s="24"/>
+      <c r="AI68" s="24"/>
+      <c r="AJ68" s="24"/>
+      <c r="AK68" s="24"/>
+      <c r="AL68" s="24"/>
+      <c r="AM68" s="24"/>
+      <c r="AN68" s="24"/>
+      <c r="AO68" s="24"/>
+      <c r="AP68" s="24"/>
     </row>
     <row r="69" spans="1:42" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="20" t="s">
@@ -48213,21 +48253,21 @@
       <c r="AA69" s="21"/>
       <c r="AB69" s="21"/>
       <c r="AC69" s="21"/>
-      <c r="AD69" s="22" t="s">
+      <c r="AD69" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="AE69" s="22"/>
-      <c r="AF69" s="22"/>
-      <c r="AG69" s="22"/>
-      <c r="AH69" s="22"/>
-      <c r="AI69" s="22"/>
-      <c r="AJ69" s="22"/>
-      <c r="AK69" s="22"/>
-      <c r="AL69" s="22"/>
-      <c r="AM69" s="22"/>
-      <c r="AN69" s="22"/>
-      <c r="AO69" s="22"/>
-      <c r="AP69" s="23"/>
+      <c r="AE69" s="25"/>
+      <c r="AF69" s="25"/>
+      <c r="AG69" s="25"/>
+      <c r="AH69" s="25"/>
+      <c r="AI69" s="25"/>
+      <c r="AJ69" s="25"/>
+      <c r="AK69" s="25"/>
+      <c r="AL69" s="25"/>
+      <c r="AM69" s="25"/>
+      <c r="AN69" s="25"/>
+      <c r="AO69" s="25"/>
+      <c r="AP69" s="26"/>
     </row>
     <row r="74" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="75" spans="1:42" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -48391,50 +48431,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:42" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="24"/>
-      <c r="AA2" s="24"/>
-      <c r="AB2" s="24"/>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="24"/>
-      <c r="AF2" s="24"/>
-      <c r="AG2" s="24"/>
-      <c r="AH2" s="24"/>
-      <c r="AI2" s="24"/>
-      <c r="AJ2" s="24"/>
-      <c r="AK2" s="24"/>
-      <c r="AL2" s="24"/>
-      <c r="AM2" s="24"/>
-      <c r="AN2" s="24"/>
-      <c r="AO2" s="24"/>
-      <c r="AP2" s="24"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="23"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
+      <c r="AH2" s="23"/>
+      <c r="AI2" s="23"/>
+      <c r="AJ2" s="23"/>
+      <c r="AK2" s="23"/>
+      <c r="AL2" s="23"/>
+      <c r="AM2" s="23"/>
+      <c r="AN2" s="23"/>
+      <c r="AO2" s="23"/>
+      <c r="AP2" s="23"/>
     </row>
     <row r="3" spans="1:42" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
@@ -48484,7 +48524,7 @@
       <c r="AM3" s="21"/>
       <c r="AN3" s="21"/>
       <c r="AO3" s="21"/>
-      <c r="AP3" s="26"/>
+      <c r="AP3" s="22"/>
     </row>
     <row r="7" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:42" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -48690,50 +48730,50 @@
       </c>
     </row>
     <row r="35" spans="1:42" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="25" t="s">
+      <c r="A35" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="25"/>
-      <c r="K35" s="25"/>
-      <c r="L35" s="25"/>
-      <c r="M35" s="25"/>
-      <c r="N35" s="25"/>
-      <c r="O35" s="25"/>
-      <c r="P35" s="25"/>
-      <c r="Q35" s="25"/>
-      <c r="R35" s="25"/>
-      <c r="S35" s="25"/>
-      <c r="T35" s="25"/>
-      <c r="U35" s="25"/>
-      <c r="V35" s="25"/>
-      <c r="W35" s="25"/>
-      <c r="X35" s="25"/>
-      <c r="Y35" s="25"/>
-      <c r="Z35" s="25"/>
-      <c r="AA35" s="25"/>
-      <c r="AB35" s="25"/>
-      <c r="AC35" s="25"/>
-      <c r="AD35" s="25"/>
-      <c r="AE35" s="25"/>
-      <c r="AF35" s="25"/>
-      <c r="AG35" s="25"/>
-      <c r="AH35" s="25"/>
-      <c r="AI35" s="25"/>
-      <c r="AJ35" s="25"/>
-      <c r="AK35" s="25"/>
-      <c r="AL35" s="25"/>
-      <c r="AM35" s="25"/>
-      <c r="AN35" s="25"/>
-      <c r="AO35" s="25"/>
-      <c r="AP35" s="25"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="24"/>
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24"/>
+      <c r="N35" s="24"/>
+      <c r="O35" s="24"/>
+      <c r="P35" s="24"/>
+      <c r="Q35" s="24"/>
+      <c r="R35" s="24"/>
+      <c r="S35" s="24"/>
+      <c r="T35" s="24"/>
+      <c r="U35" s="24"/>
+      <c r="V35" s="24"/>
+      <c r="W35" s="24"/>
+      <c r="X35" s="24"/>
+      <c r="Y35" s="24"/>
+      <c r="Z35" s="24"/>
+      <c r="AA35" s="24"/>
+      <c r="AB35" s="24"/>
+      <c r="AC35" s="24"/>
+      <c r="AD35" s="24"/>
+      <c r="AE35" s="24"/>
+      <c r="AF35" s="24"/>
+      <c r="AG35" s="24"/>
+      <c r="AH35" s="24"/>
+      <c r="AI35" s="24"/>
+      <c r="AJ35" s="24"/>
+      <c r="AK35" s="24"/>
+      <c r="AL35" s="24"/>
+      <c r="AM35" s="24"/>
+      <c r="AN35" s="24"/>
+      <c r="AO35" s="24"/>
+      <c r="AP35" s="24"/>
     </row>
     <row r="36" spans="1:42" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="20" t="s">
@@ -48769,21 +48809,21 @@
       <c r="AA36" s="21"/>
       <c r="AB36" s="21"/>
       <c r="AC36" s="21"/>
-      <c r="AD36" s="22" t="s">
+      <c r="AD36" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="AE36" s="22"/>
-      <c r="AF36" s="22"/>
-      <c r="AG36" s="22"/>
-      <c r="AH36" s="22"/>
-      <c r="AI36" s="22"/>
-      <c r="AJ36" s="22"/>
-      <c r="AK36" s="22"/>
-      <c r="AL36" s="22"/>
-      <c r="AM36" s="22"/>
-      <c r="AN36" s="22"/>
-      <c r="AO36" s="22"/>
-      <c r="AP36" s="23"/>
+      <c r="AE36" s="25"/>
+      <c r="AF36" s="25"/>
+      <c r="AG36" s="25"/>
+      <c r="AH36" s="25"/>
+      <c r="AI36" s="25"/>
+      <c r="AJ36" s="25"/>
+      <c r="AK36" s="25"/>
+      <c r="AL36" s="25"/>
+      <c r="AM36" s="25"/>
+      <c r="AN36" s="25"/>
+      <c r="AO36" s="25"/>
+      <c r="AP36" s="26"/>
     </row>
     <row r="41" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="42" spans="1:42" ht="22.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -48989,50 +49029,50 @@
       </c>
     </row>
     <row r="68" spans="1:42" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="25" t="s">
+      <c r="A68" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B68" s="25"/>
-      <c r="C68" s="25"/>
-      <c r="D68" s="25"/>
-      <c r="E68" s="25"/>
-      <c r="F68" s="25"/>
-      <c r="G68" s="25"/>
-      <c r="H68" s="25"/>
-      <c r="I68" s="25"/>
-      <c r="J68" s="25"/>
-      <c r="K68" s="25"/>
-      <c r="L68" s="25"/>
-      <c r="M68" s="25"/>
-      <c r="N68" s="25"/>
-      <c r="O68" s="25"/>
-      <c r="P68" s="25"/>
-      <c r="Q68" s="25"/>
-      <c r="R68" s="25"/>
-      <c r="S68" s="25"/>
-      <c r="T68" s="25"/>
-      <c r="U68" s="25"/>
-      <c r="V68" s="25"/>
-      <c r="W68" s="25"/>
-      <c r="X68" s="25"/>
-      <c r="Y68" s="25"/>
-      <c r="Z68" s="25"/>
-      <c r="AA68" s="25"/>
-      <c r="AB68" s="25"/>
-      <c r="AC68" s="25"/>
-      <c r="AD68" s="25"/>
-      <c r="AE68" s="25"/>
-      <c r="AF68" s="25"/>
-      <c r="AG68" s="25"/>
-      <c r="AH68" s="25"/>
-      <c r="AI68" s="25"/>
-      <c r="AJ68" s="25"/>
-      <c r="AK68" s="25"/>
-      <c r="AL68" s="25"/>
-      <c r="AM68" s="25"/>
-      <c r="AN68" s="25"/>
-      <c r="AO68" s="25"/>
-      <c r="AP68" s="25"/>
+      <c r="B68" s="24"/>
+      <c r="C68" s="24"/>
+      <c r="D68" s="24"/>
+      <c r="E68" s="24"/>
+      <c r="F68" s="24"/>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="24"/>
+      <c r="J68" s="24"/>
+      <c r="K68" s="24"/>
+      <c r="L68" s="24"/>
+      <c r="M68" s="24"/>
+      <c r="N68" s="24"/>
+      <c r="O68" s="24"/>
+      <c r="P68" s="24"/>
+      <c r="Q68" s="24"/>
+      <c r="R68" s="24"/>
+      <c r="S68" s="24"/>
+      <c r="T68" s="24"/>
+      <c r="U68" s="24"/>
+      <c r="V68" s="24"/>
+      <c r="W68" s="24"/>
+      <c r="X68" s="24"/>
+      <c r="Y68" s="24"/>
+      <c r="Z68" s="24"/>
+      <c r="AA68" s="24"/>
+      <c r="AB68" s="24"/>
+      <c r="AC68" s="24"/>
+      <c r="AD68" s="24"/>
+      <c r="AE68" s="24"/>
+      <c r="AF68" s="24"/>
+      <c r="AG68" s="24"/>
+      <c r="AH68" s="24"/>
+      <c r="AI68" s="24"/>
+      <c r="AJ68" s="24"/>
+      <c r="AK68" s="24"/>
+      <c r="AL68" s="24"/>
+      <c r="AM68" s="24"/>
+      <c r="AN68" s="24"/>
+      <c r="AO68" s="24"/>
+      <c r="AP68" s="24"/>
     </row>
     <row r="69" spans="1:42" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="20" t="s">
@@ -49082,7 +49122,7 @@
       <c r="AM69" s="21"/>
       <c r="AN69" s="21"/>
       <c r="AO69" s="21"/>
-      <c r="AP69" s="26"/>
+      <c r="AP69" s="22"/>
     </row>
     <row r="74" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="75" spans="1:42" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -49289,18 +49329,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A35:AP35"/>
+    <mergeCell ref="A2:AP2"/>
+    <mergeCell ref="A68:AP68"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:AC3"/>
+    <mergeCell ref="AD3:AP3"/>
     <mergeCell ref="A69:M69"/>
     <mergeCell ref="N69:AC69"/>
     <mergeCell ref="AD69:AP69"/>
     <mergeCell ref="A36:M36"/>
     <mergeCell ref="N36:AC36"/>
     <mergeCell ref="AD36:AP36"/>
-    <mergeCell ref="A35:AP35"/>
-    <mergeCell ref="A2:AP2"/>
-    <mergeCell ref="A68:AP68"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="N3:AC3"/>
-    <mergeCell ref="AD3:AP3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -49328,50 +49368,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:42" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="24"/>
-      <c r="AA2" s="24"/>
-      <c r="AB2" s="24"/>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="24"/>
-      <c r="AF2" s="24"/>
-      <c r="AG2" s="24"/>
-      <c r="AH2" s="24"/>
-      <c r="AI2" s="24"/>
-      <c r="AJ2" s="24"/>
-      <c r="AK2" s="24"/>
-      <c r="AL2" s="24"/>
-      <c r="AM2" s="24"/>
-      <c r="AN2" s="24"/>
-      <c r="AO2" s="24"/>
-      <c r="AP2" s="24"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="23"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
+      <c r="AH2" s="23"/>
+      <c r="AI2" s="23"/>
+      <c r="AJ2" s="23"/>
+      <c r="AK2" s="23"/>
+      <c r="AL2" s="23"/>
+      <c r="AM2" s="23"/>
+      <c r="AN2" s="23"/>
+      <c r="AO2" s="23"/>
+      <c r="AP2" s="23"/>
     </row>
     <row r="3" spans="1:42" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
@@ -49421,7 +49461,7 @@
       <c r="AM3" s="21"/>
       <c r="AN3" s="21"/>
       <c r="AO3" s="21"/>
-      <c r="AP3" s="26"/>
+      <c r="AP3" s="22"/>
     </row>
     <row r="7" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:42" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -49437,7 +49477,7 @@
       <c r="Q8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AF8" s="5" t="s">
+      <c r="AF8" s="29" t="s">
         <v>8</v>
       </c>
       <c r="AG8" s="1" t="s">
@@ -49455,14 +49495,14 @@
       <c r="P9" s="4">
         <v>1</v>
       </c>
-      <c r="Q9" s="4">
-        <v>65536</v>
+      <c r="Q9" s="31">
+        <v>131072</v>
       </c>
       <c r="AF9" s="6">
         <v>1</v>
       </c>
-      <c r="AG9" s="6">
-        <v>138440</v>
+      <c r="AG9" s="4">
+        <v>147656</v>
       </c>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.3">
@@ -49475,14 +49515,14 @@
       <c r="P10" s="6">
         <v>2</v>
       </c>
-      <c r="Q10" s="6">
-        <v>121472</v>
+      <c r="Q10" s="30">
+        <v>108872</v>
       </c>
       <c r="AF10" s="6">
         <v>2</v>
       </c>
       <c r="AG10" s="6">
-        <v>163616</v>
+        <v>203120</v>
       </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.3">
@@ -49495,14 +49535,14 @@
       <c r="P11" s="6">
         <v>3</v>
       </c>
-      <c r="Q11" s="6">
-        <v>77164</v>
+      <c r="Q11" s="30">
+        <v>83868</v>
       </c>
       <c r="AF11" s="6">
         <v>3</v>
       </c>
       <c r="AG11" s="6">
-        <v>165480</v>
+        <v>241968</v>
       </c>
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.3">
@@ -49515,14 +49555,14 @@
       <c r="P12" s="6">
         <v>4</v>
       </c>
-      <c r="Q12" s="6">
-        <v>95748</v>
+      <c r="Q12" s="30">
+        <v>91320</v>
       </c>
       <c r="AF12" s="6">
         <v>4</v>
       </c>
       <c r="AG12" s="6">
-        <v>206256</v>
+        <v>233496</v>
       </c>
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.3">
@@ -49535,14 +49575,14 @@
       <c r="P13" s="6">
         <v>5</v>
       </c>
-      <c r="Q13" s="6">
-        <v>68892</v>
+      <c r="Q13" s="30">
+        <v>58356</v>
       </c>
       <c r="AF13" s="6">
         <v>5</v>
       </c>
       <c r="AG13" s="6">
-        <v>184488</v>
+        <v>168624</v>
       </c>
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.3">
@@ -49555,14 +49595,14 @@
       <c r="P14" s="6">
         <v>6</v>
       </c>
-      <c r="Q14" s="6">
-        <v>58044</v>
+      <c r="Q14" s="30">
+        <v>77712</v>
       </c>
       <c r="AF14" s="6">
         <v>6</v>
       </c>
       <c r="AG14" s="6">
-        <v>144264</v>
+        <v>35328</v>
       </c>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.3">
@@ -49575,14 +49615,14 @@
       <c r="P15" s="6">
         <v>7</v>
       </c>
-      <c r="Q15" s="6">
-        <v>70776</v>
+      <c r="Q15" s="30">
+        <v>75120</v>
       </c>
       <c r="AF15" s="6">
         <v>7</v>
       </c>
       <c r="AG15" s="6">
-        <v>31104</v>
+        <v>16944</v>
       </c>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.3">
@@ -49595,14 +49635,14 @@
       <c r="P16" s="6">
         <v>8</v>
       </c>
-      <c r="Q16" s="6">
-        <v>87768</v>
-      </c>
-      <c r="AF16" s="6">
+      <c r="Q16" s="30">
+        <v>58008</v>
+      </c>
+      <c r="AF16" s="28">
         <v>8</v>
       </c>
-      <c r="AG16" s="6">
-        <v>13632</v>
+      <c r="AG16" s="28">
+        <v>1440</v>
       </c>
     </row>
     <row r="17" spans="2:33" x14ac:dyDescent="0.3">
@@ -49615,14 +49655,14 @@
       <c r="P17" s="6">
         <v>9</v>
       </c>
-      <c r="Q17" s="6">
-        <v>38928</v>
-      </c>
-      <c r="AF17" s="14">
+      <c r="Q17" s="30">
+        <v>38784</v>
+      </c>
+      <c r="AF17" s="27">
         <v>9</v>
       </c>
-      <c r="AG17" s="14">
-        <v>1296</v>
+      <c r="AG17" s="27">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:33" x14ac:dyDescent="0.3">
@@ -49635,8 +49675,8 @@
       <c r="P18" s="6">
         <v>10</v>
       </c>
-      <c r="Q18" s="6">
-        <v>38784</v>
+      <c r="Q18" s="30">
+        <v>62712</v>
       </c>
       <c r="AF18" s="6">
         <v>10</v>
@@ -49655,8 +49695,8 @@
       <c r="P19" s="6">
         <v>11</v>
       </c>
-      <c r="Q19" s="6">
-        <v>62712</v>
+      <c r="Q19" s="30">
+        <v>61176</v>
       </c>
       <c r="AF19" s="6">
         <v>11</v>
@@ -49675,8 +49715,8 @@
       <c r="P20" s="6">
         <v>12</v>
       </c>
-      <c r="Q20" s="6">
-        <v>61176</v>
+      <c r="Q20" s="30">
+        <v>35760</v>
       </c>
       <c r="AF20" s="6">
         <v>12</v>
@@ -49699,8 +49739,8 @@
       <c r="P21" s="6">
         <v>13</v>
       </c>
-      <c r="Q21" s="6">
-        <v>35760</v>
+      <c r="Q21" s="30">
+        <v>66864</v>
       </c>
       <c r="AF21" s="6">
         <v>13</v>
@@ -49723,8 +49763,8 @@
       <c r="P22" s="6">
         <v>14</v>
       </c>
-      <c r="Q22" s="6">
-        <v>66864</v>
+      <c r="Q22" s="30">
+        <v>19104</v>
       </c>
       <c r="AF22" s="6">
         <v>14</v>
@@ -49743,8 +49783,8 @@
       <c r="P23" s="6">
         <v>15</v>
       </c>
-      <c r="Q23" s="6">
-        <v>19104</v>
+      <c r="Q23" s="30">
+        <v>79848</v>
       </c>
       <c r="AF23" s="6">
         <v>15</v>
@@ -49764,7 +49804,7 @@
         <v>16</v>
       </c>
       <c r="Q24" s="6">
-        <v>79848</v>
+        <v>0</v>
       </c>
       <c r="AF24" s="6">
         <v>16</v>
@@ -49783,50 +49823,50 @@
       </c>
     </row>
     <row r="39" spans="1:42" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="25" t="s">
+      <c r="A39" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="25"/>
-      <c r="J39" s="25"/>
-      <c r="K39" s="25"/>
-      <c r="L39" s="25"/>
-      <c r="M39" s="25"/>
-      <c r="N39" s="25"/>
-      <c r="O39" s="25"/>
-      <c r="P39" s="25"/>
-      <c r="Q39" s="25"/>
-      <c r="R39" s="25"/>
-      <c r="S39" s="25"/>
-      <c r="T39" s="25"/>
-      <c r="U39" s="25"/>
-      <c r="V39" s="25"/>
-      <c r="W39" s="25"/>
-      <c r="X39" s="25"/>
-      <c r="Y39" s="25"/>
-      <c r="Z39" s="25"/>
-      <c r="AA39" s="25"/>
-      <c r="AB39" s="25"/>
-      <c r="AC39" s="25"/>
-      <c r="AD39" s="25"/>
-      <c r="AE39" s="25"/>
-      <c r="AF39" s="25"/>
-      <c r="AG39" s="25"/>
-      <c r="AH39" s="25"/>
-      <c r="AI39" s="25"/>
-      <c r="AJ39" s="25"/>
-      <c r="AK39" s="25"/>
-      <c r="AL39" s="25"/>
-      <c r="AM39" s="25"/>
-      <c r="AN39" s="25"/>
-      <c r="AO39" s="25"/>
-      <c r="AP39" s="25"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="24"/>
+      <c r="J39" s="24"/>
+      <c r="K39" s="24"/>
+      <c r="L39" s="24"/>
+      <c r="M39" s="24"/>
+      <c r="N39" s="24"/>
+      <c r="O39" s="24"/>
+      <c r="P39" s="24"/>
+      <c r="Q39" s="24"/>
+      <c r="R39" s="24"/>
+      <c r="S39" s="24"/>
+      <c r="T39" s="24"/>
+      <c r="U39" s="24"/>
+      <c r="V39" s="24"/>
+      <c r="W39" s="24"/>
+      <c r="X39" s="24"/>
+      <c r="Y39" s="24"/>
+      <c r="Z39" s="24"/>
+      <c r="AA39" s="24"/>
+      <c r="AB39" s="24"/>
+      <c r="AC39" s="24"/>
+      <c r="AD39" s="24"/>
+      <c r="AE39" s="24"/>
+      <c r="AF39" s="24"/>
+      <c r="AG39" s="24"/>
+      <c r="AH39" s="24"/>
+      <c r="AI39" s="24"/>
+      <c r="AJ39" s="24"/>
+      <c r="AK39" s="24"/>
+      <c r="AL39" s="24"/>
+      <c r="AM39" s="24"/>
+      <c r="AN39" s="24"/>
+      <c r="AO39" s="24"/>
+      <c r="AP39" s="24"/>
     </row>
     <row r="40" spans="1:42" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="20" t="s">
@@ -49876,7 +49916,7 @@
       <c r="AM40" s="21"/>
       <c r="AN40" s="21"/>
       <c r="AO40" s="21"/>
-      <c r="AP40" s="26"/>
+      <c r="AP40" s="22"/>
     </row>
     <row r="45" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="46" spans="1:42" ht="22.2" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -50256,7 +50296,8 @@
     <mergeCell ref="AD3:AP3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -50281,50 +50322,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:42" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="24"/>
-      <c r="AA2" s="24"/>
-      <c r="AB2" s="24"/>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="24"/>
-      <c r="AF2" s="24"/>
-      <c r="AG2" s="24"/>
-      <c r="AH2" s="24"/>
-      <c r="AI2" s="24"/>
-      <c r="AJ2" s="24"/>
-      <c r="AK2" s="24"/>
-      <c r="AL2" s="24"/>
-      <c r="AM2" s="24"/>
-      <c r="AN2" s="24"/>
-      <c r="AO2" s="24"/>
-      <c r="AP2" s="24"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="23"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
+      <c r="AH2" s="23"/>
+      <c r="AI2" s="23"/>
+      <c r="AJ2" s="23"/>
+      <c r="AK2" s="23"/>
+      <c r="AL2" s="23"/>
+      <c r="AM2" s="23"/>
+      <c r="AN2" s="23"/>
+      <c r="AO2" s="23"/>
+      <c r="AP2" s="23"/>
     </row>
     <row r="3" spans="1:42" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
@@ -50374,7 +50415,7 @@
       <c r="AM3" s="21"/>
       <c r="AN3" s="21"/>
       <c r="AO3" s="21"/>
-      <c r="AP3" s="26"/>
+      <c r="AP3" s="22"/>
     </row>
     <row r="7" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:42" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -51139,50 +51180,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:42" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="24"/>
-      <c r="AA2" s="24"/>
-      <c r="AB2" s="24"/>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="24"/>
-      <c r="AF2" s="24"/>
-      <c r="AG2" s="24"/>
-      <c r="AH2" s="24"/>
-      <c r="AI2" s="24"/>
-      <c r="AJ2" s="24"/>
-      <c r="AK2" s="24"/>
-      <c r="AL2" s="24"/>
-      <c r="AM2" s="24"/>
-      <c r="AN2" s="24"/>
-      <c r="AO2" s="24"/>
-      <c r="AP2" s="24"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="23"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
+      <c r="AH2" s="23"/>
+      <c r="AI2" s="23"/>
+      <c r="AJ2" s="23"/>
+      <c r="AK2" s="23"/>
+      <c r="AL2" s="23"/>
+      <c r="AM2" s="23"/>
+      <c r="AN2" s="23"/>
+      <c r="AO2" s="23"/>
+      <c r="AP2" s="23"/>
     </row>
     <row r="3" spans="1:42" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
@@ -51232,7 +51273,7 @@
       <c r="AM3" s="21"/>
       <c r="AN3" s="21"/>
       <c r="AO3" s="21"/>
-      <c r="AP3" s="26"/>
+      <c r="AP3" s="22"/>
     </row>
     <row r="7" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:42" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -52778,50 +52819,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:42" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="24"/>
-      <c r="AA2" s="24"/>
-      <c r="AB2" s="24"/>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="24"/>
-      <c r="AF2" s="24"/>
-      <c r="AG2" s="24"/>
-      <c r="AH2" s="24"/>
-      <c r="AI2" s="24"/>
-      <c r="AJ2" s="24"/>
-      <c r="AK2" s="24"/>
-      <c r="AL2" s="24"/>
-      <c r="AM2" s="24"/>
-      <c r="AN2" s="24"/>
-      <c r="AO2" s="24"/>
-      <c r="AP2" s="24"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="23"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
+      <c r="AH2" s="23"/>
+      <c r="AI2" s="23"/>
+      <c r="AJ2" s="23"/>
+      <c r="AK2" s="23"/>
+      <c r="AL2" s="23"/>
+      <c r="AM2" s="23"/>
+      <c r="AN2" s="23"/>
+      <c r="AO2" s="23"/>
+      <c r="AP2" s="23"/>
     </row>
     <row r="3" spans="1:42" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
@@ -52871,7 +52912,7 @@
       <c r="AM3" s="21"/>
       <c r="AN3" s="21"/>
       <c r="AO3" s="21"/>
-      <c r="AP3" s="26"/>
+      <c r="AP3" s="22"/>
     </row>
     <row r="7" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:42" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
